--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -2125,17 +2125,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2177,426 +2177,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
         </is>
       </c>
     </row>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -53,7 +53,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FFC000"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,7 +61,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFC000"/>
+      <color rgb="0000E676"/>
     </font>
   </fonts>
   <fills count="5">
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -624,12 +624,12 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -644,15 +644,19 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -660,12 +664,12 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr"/>
@@ -674,12 +678,12 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -694,15 +698,19 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -710,12 +718,12 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr"/>
@@ -724,10 +732,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -749,7 +757,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -764,12 +772,12 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr"/>
@@ -778,10 +786,10 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -803,12 +811,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro, exclusive</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -818,7 +826,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -832,10 +840,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -882,12 +890,12 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -907,12 +915,12 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -927,7 +935,7 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
@@ -936,10 +944,10 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -961,14 +969,10 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -981,7 +985,7 @@
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr"/>
@@ -990,12 +994,12 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1015,10 +1019,14 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1031,7 +1039,7 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr"/>
@@ -1040,10 +1048,10 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1060,17 +1068,17 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1085,7 +1093,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr"/>
@@ -1094,10 +1102,10 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1119,12 +1127,12 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1139,7 +1147,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr"/>
@@ -1151,7 +1159,7 @@
         <v>46095</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1173,7 +1181,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -1199,60 +1207,6 @@
       <c r="L14" s="10" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1269,10 +1223,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1291,7 +1245,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>March 2026 - April 2026 Shoe Releases</t>
+          <t>March 2026 Shoe Releases</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1330,12 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1396,15 +1350,19 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1412,12 +1370,12 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr"/>
@@ -1426,12 +1384,12 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1446,15 +1404,19 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1462,12 +1424,12 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr"/>
@@ -1476,10 +1438,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1501,7 +1463,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1516,12 +1478,12 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr"/>
@@ -1530,10 +1492,10 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1555,12 +1517,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro, exclusive</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1570,7 +1532,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -1584,10 +1546,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1634,12 +1596,12 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1659,12 +1621,12 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1679,7 +1641,7 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
@@ -1688,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1713,14 +1675,10 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1733,7 +1691,7 @@
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr"/>
@@ -1742,12 +1700,12 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1767,10 +1725,14 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1783,7 +1745,7 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr"/>
@@ -1792,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1812,17 +1774,17 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1837,7 +1799,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr"/>
@@ -1846,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1871,12 +1833,12 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1891,7 +1853,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr"/>
@@ -1903,7 +1865,7 @@
         <v>46095</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1925,7 +1887,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -1951,164 +1913,6 @@
       <c r="L14" s="10" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2125,17 +1929,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2177,6 +1981,516 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Neon Yellow</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2296,14 +2610,14 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2318,15 +2632,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2334,18 +2652,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
         <v>50</v>
@@ -2354,14 +2672,14 @@
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2376,15 +2694,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2392,18 +2714,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="O3" t="n">
         <v>50</v>
@@ -2412,7 +2734,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -2439,7 +2761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2454,12 +2776,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -2474,7 +2796,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -2501,12 +2823,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro, exclusive</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2516,7 +2838,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2536,7 +2858,7 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -2594,14 +2916,14 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2621,12 +2943,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2641,13 +2963,13 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>50</v>
@@ -2656,7 +2978,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -2683,14 +3005,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2703,7 +3021,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -2718,14 +3036,14 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2745,10 +3063,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2761,13 +3083,13 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
         <v>50</v>
@@ -2776,7 +3098,7 @@
     </row>
     <row r="10">
       <c r="A10" s="13" t="n">
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -2798,17 +3120,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2823,7 +3145,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -2838,7 +3160,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -2865,12 +3187,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2885,13 +3207,13 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
         <v>50</v>
@@ -2927,7 +3249,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2959,188 +3281,6 @@
         <v>50</v>
       </c>
       <c r="P12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>22</v>
-      </c>
-      <c r="O13" t="n">
-        <v>50</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>12</v>
-      </c>
-      <c r="O14" t="n">
-        <v>50</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>12</v>
-      </c>
-      <c r="O15" t="n">
-        <v>50</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3265,7 +3405,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="12" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="9" t="n"/>
@@ -3315,7 +3455,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3325,7 +3465,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5"/>
@@ -3353,7 +3493,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3363,7 +3503,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10"/>
@@ -3391,7 +3531,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -3401,7 +3541,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15"/>
@@ -3429,7 +3569,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -57,7 +57,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007CFCFF"/>
+      <color rgb="00FFD966"/>
     </font>
     <font>
       <b val="1"/>
@@ -65,7 +65,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFD966"/>
+      <color rgb="007CFCFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -643,9 +643,7 @@
       <c r="A4" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -653,7 +651,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -698,9 +696,7 @@
       <c r="A5" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -708,7 +704,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -759,7 +755,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -810,9 +806,7 @@
       <c r="A7" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -820,12 +814,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -869,9 +863,7 @@
       <c r="A8" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -879,12 +871,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -928,9 +920,7 @@
       <c r="A9" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -938,7 +928,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -987,15 +977,13 @@
       <c r="A10" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1046,15 +1034,13 @@
       <c r="A11" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1105,9 +1091,7 @@
       <c r="A12" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1115,7 +1099,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1160,9 +1144,7 @@
       <c r="A13" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1170,7 +1152,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1215,9 +1197,7 @@
       <c r="A14" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1225,7 +1205,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1270,9 +1250,7 @@
       <c r="A15" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1280,7 +1258,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1325,9 +1303,7 @@
       <c r="A16" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1335,7 +1311,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1380,9 +1356,7 @@
       <c r="A17" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1390,7 +1364,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1435,9 +1409,7 @@
       <c r="A18" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -1445,12 +1417,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1500,7 +1472,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1551,9 +1523,7 @@
       <c r="A20" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1561,7 +1531,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1610,9 +1580,7 @@
       <c r="A21" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1620,7 +1588,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1665,9 +1633,7 @@
       <c r="A22" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -1675,12 +1641,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -1730,7 +1696,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1781,9 +1747,7 @@
       <c r="A24" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -1791,12 +1755,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -1840,9 +1804,7 @@
       <c r="A25" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1850,7 +1812,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1895,15 +1857,13 @@
       <c r="A26" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1950,9 +1910,7 @@
       <c r="A27" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1960,7 +1918,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2009,9 +1967,7 @@
       <c r="A28" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2019,7 +1975,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -2068,15 +2024,13 @@
       <c r="A29" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2123,9 +2077,7 @@
       <c r="A30" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2133,7 +2085,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -2188,7 +2140,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2239,9 +2191,7 @@
       <c r="A32" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2249,7 +2199,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -2294,15 +2244,13 @@
       <c r="A33" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2349,9 +2297,7 @@
       <c r="A34" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>25</v>
-      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2359,7 +2305,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -2410,7 +2356,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2463,7 +2409,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2516,7 +2462,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2573,7 +2519,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2630,7 +2576,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2687,7 +2633,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2744,7 +2690,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2801,7 +2747,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2858,7 +2804,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2915,7 +2861,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2972,7 +2918,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3029,7 +2975,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3086,7 +3032,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3143,7 +3089,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3196,7 +3142,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3253,7 +3199,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3310,7 +3256,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3367,7 +3313,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3424,7 +3370,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3477,7 +3423,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3534,7 +3480,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3587,7 +3533,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3640,7 +3586,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3697,7 +3643,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3754,7 +3700,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3811,7 +3757,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3864,7 +3810,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3917,7 +3863,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3974,7 +3920,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4027,7 +3973,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4084,7 +4030,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4141,7 +4087,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4198,7 +4144,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4255,7 +4201,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4312,7 +4258,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4365,7 +4311,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4422,7 +4368,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4479,7 +4425,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4532,7 +4478,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4589,7 +4535,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4642,7 +4588,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4695,7 +4641,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4748,7 +4694,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4801,7 +4747,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4854,7 +4800,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4911,7 +4857,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4964,7 +4910,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5017,7 +4963,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5070,7 +5016,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5127,7 +5073,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5180,7 +5126,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5237,7 +5183,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5294,7 +5240,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5351,7 +5297,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5408,7 +5354,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5465,7 +5411,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5518,7 +5464,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5691,9 +5637,7 @@
       <c r="A4" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -5701,7 +5645,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -5746,9 +5690,7 @@
       <c r="A5" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -5756,7 +5698,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -5807,7 +5749,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5858,9 +5800,7 @@
       <c r="A7" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -5868,12 +5808,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -5917,9 +5857,7 @@
       <c r="A8" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -5927,12 +5865,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -5976,9 +5914,7 @@
       <c r="A9" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -5986,7 +5922,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -6035,15 +5971,13 @@
       <c r="A10" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6094,15 +6028,13 @@
       <c r="A11" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6153,9 +6085,7 @@
       <c r="A12" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6163,7 +6093,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -6208,9 +6138,7 @@
       <c r="A13" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6218,7 +6146,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -6263,9 +6191,7 @@
       <c r="A14" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6273,7 +6199,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -6318,9 +6244,7 @@
       <c r="A15" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6328,7 +6252,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -6373,9 +6297,7 @@
       <c r="A16" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6383,7 +6305,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -6428,9 +6350,7 @@
       <c r="A17" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6438,7 +6358,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -6483,9 +6403,7 @@
       <c r="A18" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6493,12 +6411,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -6548,7 +6466,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -6599,9 +6517,7 @@
       <c r="A20" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6609,7 +6525,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -6658,9 +6574,7 @@
       <c r="A21" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6668,7 +6582,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -6713,9 +6627,7 @@
       <c r="A22" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6723,12 +6635,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -6778,7 +6690,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -6829,9 +6741,7 @@
       <c r="A24" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6839,12 +6749,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -6888,9 +6798,7 @@
       <c r="A25" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6898,7 +6806,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -6943,15 +6851,13 @@
       <c r="A26" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6998,9 +6904,7 @@
       <c r="A27" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7008,7 +6912,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -7057,9 +6961,7 @@
       <c r="A28" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7067,7 +6969,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -7116,15 +7018,13 @@
       <c r="A29" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -7171,9 +7071,7 @@
       <c r="A30" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7181,7 +7079,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -7236,7 +7134,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7287,9 +7185,7 @@
       <c r="A32" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7297,7 +7193,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -7342,15 +7238,13 @@
       <c r="A33" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -7397,9 +7291,7 @@
       <c r="A34" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>25</v>
-      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7407,7 +7299,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -7458,7 +7350,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7511,7 +7403,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7564,7 +7456,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7621,7 +7513,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7678,7 +7570,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7735,7 +7627,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7792,7 +7684,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7849,7 +7741,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7906,7 +7798,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7963,7 +7855,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8020,7 +7912,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8077,7 +7969,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8134,7 +8026,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8191,7 +8083,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8244,7 +8136,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8301,7 +8193,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8358,7 +8250,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8415,7 +8307,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8472,7 +8364,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8525,7 +8417,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8582,7 +8474,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8635,7 +8527,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8688,7 +8580,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8745,7 +8637,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8802,7 +8694,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8859,7 +8751,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8912,7 +8804,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8965,7 +8857,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9022,7 +8914,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9075,7 +8967,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9132,7 +9024,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9189,7 +9081,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9246,7 +9138,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9303,7 +9195,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9360,7 +9252,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9413,7 +9305,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9470,7 +9362,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9527,7 +9419,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9580,7 +9472,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9637,7 +9529,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9690,7 +9582,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9743,7 +9635,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9796,7 +9688,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9849,7 +9741,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9902,7 +9794,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9959,7 +9851,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10012,7 +9904,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10065,7 +9957,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10118,7 +10010,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10175,7 +10067,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10228,7 +10120,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10285,7 +10177,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10342,7 +10234,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10399,7 +10291,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -10456,7 +10348,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10513,7 +10405,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10566,7 +10458,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10619,7 +10511,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10676,7 +10568,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10729,7 +10621,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10782,7 +10674,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10839,7 +10731,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -10892,7 +10784,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10945,7 +10837,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11007,7 +10899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11015,8 +10907,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -11090,17 +10982,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11132,17 +11024,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11174,17 +11066,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11216,17 +11108,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11258,17 +11150,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11300,17 +11192,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11342,17 +11234,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11384,17 +11276,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11426,17 +11318,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11468,17 +11360,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11510,17 +11402,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11552,17 +11444,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11486,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11636,17 +11528,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11678,17 +11570,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11720,17 +11612,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11762,17 +11654,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11804,17 +11696,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11846,17 +11738,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11888,17 +11780,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11930,17 +11822,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11972,17 +11864,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12014,17 +11906,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12056,17 +11948,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12098,17 +11990,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12140,17 +12032,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12182,17 +12074,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12224,17 +12116,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12266,17 +12158,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12308,17 +12200,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12350,17 +12242,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12392,17 +12284,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12326,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12476,17 +12368,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12518,17 +12410,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12452,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12602,17 +12494,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12644,17 +12536,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12686,17 +12578,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12728,17 +12620,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12770,17 +12662,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12812,17 +12704,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12854,17 +12746,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12896,17 +12788,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12830,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12872,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13022,17 +12914,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13064,17 +12956,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13106,17 +12998,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13148,17 +13040,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13190,17 +13082,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13232,17 +13124,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13274,17 +13166,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13316,47 +13208,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13347,7 @@
         <v>46087</v>
       </c>
       <c r="B2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13494,7 +13356,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13537,7 +13399,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -13546,7 +13408,7 @@
         <v>46087</v>
       </c>
       <c r="B3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -13555,7 +13417,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13598,7 +13460,7 @@
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -13672,7 +13534,7 @@
         <v>46087</v>
       </c>
       <c r="B5" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -13681,12 +13543,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13728,7 +13590,7 @@
         <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -13737,7 +13599,7 @@
         <v>46087</v>
       </c>
       <c r="B6" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -13746,12 +13608,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13793,7 +13655,7 @@
         <v>22</v>
       </c>
       <c r="P6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -13802,7 +13664,7 @@
         <v>46087</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -13811,7 +13673,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13858,7 +13720,7 @@
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -13867,7 +13729,7 @@
         <v>46087</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -13923,7 +13785,7 @@
         <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -13932,7 +13794,7 @@
         <v>46087</v>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -13988,7 +13850,7 @@
         <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -13997,7 +13859,7 @@
         <v>46087</v>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -14006,7 +13868,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -14049,7 +13911,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -14058,7 +13920,7 @@
         <v>46087</v>
       </c>
       <c r="B11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -14067,7 +13929,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -14110,7 +13972,7 @@
         <v>12</v>
       </c>
       <c r="P11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -14119,7 +13981,7 @@
         <v>46087</v>
       </c>
       <c r="B12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -14128,7 +13990,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -14171,7 +14033,7 @@
         <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
@@ -14180,7 +14042,7 @@
         <v>46087</v>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -14189,7 +14051,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14232,7 +14094,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -14241,7 +14103,7 @@
         <v>46087</v>
       </c>
       <c r="B14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -14250,7 +14112,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -14293,7 +14155,7 @@
         <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -14302,7 +14164,7 @@
         <v>46087</v>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -14311,7 +14173,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -14354,7 +14216,7 @@
         <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -14363,7 +14225,7 @@
         <v>46087</v>
       </c>
       <c r="B16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -14372,12 +14234,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -14419,7 +14281,7 @@
         <v>22</v>
       </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -14493,7 +14355,7 @@
         <v>46087</v>
       </c>
       <c r="B18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -14502,7 +14364,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14549,7 +14411,7 @@
         <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -14558,7 +14420,7 @@
         <v>46087</v>
       </c>
       <c r="B19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -14567,7 +14429,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -14610,7 +14472,7 @@
         <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
@@ -14619,7 +14481,7 @@
         <v>46087</v>
       </c>
       <c r="B20" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -14628,12 +14490,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -14675,7 +14537,7 @@
         <v>22</v>
       </c>
       <c r="P20" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -14749,7 +14611,7 @@
         <v>46087</v>
       </c>
       <c r="B22" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -14758,12 +14620,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -14805,7 +14667,7 @@
         <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -14814,7 +14676,7 @@
         <v>46087</v>
       </c>
       <c r="B23" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -14823,7 +14685,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14866,7 +14728,7 @@
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -14875,7 +14737,7 @@
         <v>46087</v>
       </c>
       <c r="B24" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -14927,7 +14789,7 @@
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -14936,7 +14798,7 @@
         <v>46087</v>
       </c>
       <c r="B25" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -14945,7 +14807,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -14992,7 +14854,7 @@
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -15001,7 +14863,7 @@
         <v>46087</v>
       </c>
       <c r="B26" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -15010,7 +14872,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -15057,7 +14919,7 @@
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -15066,7 +14928,7 @@
         <v>46087</v>
       </c>
       <c r="B27" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -15118,7 +14980,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -15127,7 +14989,7 @@
         <v>46087</v>
       </c>
       <c r="B28" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -15136,7 +14998,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -15183,7 +15045,7 @@
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -15257,7 +15119,7 @@
         <v>46087</v>
       </c>
       <c r="B30" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -15266,7 +15128,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -15309,7 +15171,7 @@
         <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -15318,7 +15180,7 @@
         <v>46087</v>
       </c>
       <c r="B31" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -15370,7 +15232,7 @@
         <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -15379,7 +15241,7 @@
         <v>46087</v>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -15388,7 +15250,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -15428,10 +15290,10 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -19845,7 +19707,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -19855,7 +19717,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -10911,17 +10911,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10963,6 +10963,132 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Adidas Anthony Edwards 2 Georgia Bulldogs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-06T09:39:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Air Jordan 1 High OG Pale Ivory / Psychic Blue</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06T09:39:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 OG Lakers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-06T09:39:05Z</t>
         </is>
       </c>
     </row>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-grey-matter-u20004jq/705427</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-dark-team-red-patent-leather-pack-io4489-601/706787</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr"/>
@@ -714,12 +714,12 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-ice-wine-u20002t8/705920</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-mystic-navy-patent-leather-pack-io4489-400/706786</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr"/>
@@ -772,14 +772,10 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -795,7 +791,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-vomero-premium-black-iq0627-001/705450</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-topaz-gold-patent-leather-pack-io4489-700/706785</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -1198,9 +1194,9 @@
         <v>46093</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1220,12 +1216,12 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -1243,7 +1239,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -1260,9 +1256,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1277,7 +1273,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -1296,11 +1292,11 @@
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -1317,9 +1313,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1334,26 +1330,30 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -1382,23 +1382,23 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
+          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
+          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -1541,23 +1541,23 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Converse Shai 001 Pink</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -1576,7 +1576,9 @@
       <c r="A21" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>288</v>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1599,18 +1601,18 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Converse Shai 001 Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K21" s="9" t="n">
@@ -1618,7 +1620,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
+          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -1635,9 +1637,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1652,30 +1654,26 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -1692,9 +1690,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1704,12 +1702,12 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -1728,11 +1726,11 @@
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -1761,23 +1759,27 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
@@ -1785,7 +1787,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -1819,7 +1821,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr"/>
@@ -1838,7 +1840,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -1855,9 +1857,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -1872,26 +1874,26 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 Faded Black / Utility Green</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -1908,9 +1910,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1925,26 +1927,26 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>New Balance 1890 Faded Black / Utility Green</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -1956,9 +1958,9 @@
         <v>46093</v>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1973,27 +1975,23 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr"/>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K28" s="9" t="n">
@@ -2001,7 +1999,7 @@
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr"/>
@@ -2018,14 +2016,14 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -2035,30 +2033,30 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -2070,19 +2068,19 @@
         <v>46093</v>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -2092,26 +2090,30 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Kobe 3 Low Protro Pink Quartz</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -2145,7 +2147,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr"/>
@@ -2164,7 +2166,7 @@
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -2198,18 +2200,18 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -2217,7 +2219,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -4460,7 +4462,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
@@ -6108,6 +6110,173 @@
       <c r="M103" s="10" t="inlineStr"/>
       <c r="N103" s="10" t="inlineStr"/>
       <c r="O103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr"/>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-team-usa-iq0407-100/706740</t>
+        </is>
+      </c>
+      <c r="M104" s="10" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
+      <c r="O104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr"/>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>Nike Air Max 95 SE 'England'</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-se-england-iq0176-100/706661</t>
+        </is>
+      </c>
+      <c r="M105" s="10" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
+      <c r="O105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr"/>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-air-max-plus-french-football-federation-iq0170-400/706739</t>
+        </is>
+      </c>
+      <c r="M106" s="10" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
+      <c r="O106" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6124,7 +6293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -6257,12 +6426,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr"/>
@@ -6281,7 +6450,7 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-grey-matter-u20004jq/705427</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-dark-team-red-patent-leather-pack-io4489-601/706787</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr"/>
@@ -6310,12 +6479,12 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr"/>
@@ -6334,7 +6503,7 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-ice-wine-u20002t8/705920</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-mystic-navy-patent-leather-pack-io4489-400/706786</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr"/>
@@ -6368,14 +6537,10 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -6391,7 +6556,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-vomero-premium-black-iq0627-001/705450</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-topaz-gold-patent-leather-pack-io4489-700/706785</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -6794,9 +6959,9 @@
         <v>46093</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -6816,12 +6981,12 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -6839,7 +7004,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -6856,9 +7021,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -6873,7 +7038,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -6892,11 +7057,11 @@
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -6913,9 +7078,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -6930,26 +7095,30 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -6978,23 +7147,23 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
@@ -7002,7 +7171,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
+          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -7036,7 +7205,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
+          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -7055,7 +7224,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -7089,7 +7258,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr"/>
@@ -7108,7 +7277,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -7137,23 +7306,23 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Converse Shai 001 Pink</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
@@ -7161,7 +7330,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -7172,7 +7341,9 @@
       <c r="A21" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>288</v>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7195,18 +7366,18 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Converse Shai 001 Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K21" s="9" t="n">
@@ -7214,7 +7385,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
+          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -7231,9 +7402,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -7248,30 +7419,26 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -7288,9 +7455,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -7300,12 +7467,12 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -7324,11 +7491,11 @@
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -7357,23 +7524,27 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
@@ -7381,7 +7552,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -7415,7 +7586,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr"/>
@@ -7434,7 +7605,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -7451,9 +7622,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -7468,26 +7639,26 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 Faded Black / Utility Green</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -7504,9 +7675,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -7521,26 +7692,26 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>New Balance 1890 Faded Black / Utility Green</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -7552,9 +7723,9 @@
         <v>46093</v>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -7569,27 +7740,23 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr"/>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K28" s="9" t="n">
@@ -7597,7 +7764,7 @@
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr"/>
@@ -7614,14 +7781,14 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -7631,30 +7798,30 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -7666,19 +7833,19 @@
         <v>46093</v>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -7688,26 +7855,30 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Kobe 3 Low Protro Pink Quartz</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -7741,7 +7912,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr"/>
@@ -7760,7 +7931,7 @@
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -7794,18 +7965,18 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -7813,7 +7984,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -10056,7 +10227,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
@@ -11707,7 +11878,7 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B104" s="5" t="inlineStr"/>
       <c r="C104" s="6" t="inlineStr">
@@ -11727,12 +11898,12 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr"/>
@@ -11751,7 +11922,7 @@
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-team-usa-iq0407-100/706740</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr"/>
@@ -11760,12 +11931,12 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B105" s="5" t="inlineStr"/>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -11780,15 +11951,19 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr"/>
+          <t>Nike Air Max 95 SE 'England'</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -11804,7 +11979,7 @@
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-se-england-iq0176-100/706661</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr"/>
@@ -11813,12 +11988,12 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B106" s="5" t="inlineStr"/>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -11838,12 +12013,12 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
@@ -11861,7 +12036,7 @@
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-plus-french-football-federation-iq0170-400/706739</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr"/>
@@ -11890,12 +12065,12 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr"/>
@@ -11914,7 +12089,7 @@
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr"/>
@@ -11926,9 +12101,9 @@
         <v>46107</v>
       </c>
       <c r="B108" s="5" t="inlineStr"/>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -11943,19 +12118,15 @@
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>collab, running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr"/>
       <c r="I108" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -11971,7 +12142,7 @@
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr"/>
@@ -11980,12 +12151,12 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B109" s="5" t="inlineStr"/>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -12005,18 +12176,22 @@
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr"/>
+          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K109" s="9" t="n">
@@ -12024,7 +12199,7 @@
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr"/>
@@ -12033,7 +12208,7 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B110" s="5" t="inlineStr"/>
       <c r="C110" s="6" t="inlineStr">
@@ -12058,7 +12233,7 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr"/>
@@ -12077,12 +12252,122 @@
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr"/>
       <c r="N110" s="10" t="inlineStr"/>
       <c r="O110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr"/>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>collab, running, exclusive</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+        </is>
+      </c>
+      <c r="M111" s="10" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr"/>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr"/>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M112" s="10" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
+      <c r="O112" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12099,13 +12384,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -12157,12 +12442,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12172,7 +12457,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -12180,14 +12465,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12197,12 +12482,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -12210,14 +12495,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12227,12 +12512,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -12240,7 +12525,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12257,12 +12542,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -12270,7 +12555,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12287,12 +12572,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -12300,7 +12585,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12317,12 +12602,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Nike Vomero Premium 'Black' From £ 200</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -12330,29 +12615,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -12360,14 +12645,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12377,12 +12662,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -12390,14 +12675,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12407,32 +12692,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Nike Sabrina 3 Oregon Ducks</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12442,27 +12739,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Air Jordan 13 Chicago</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12472,15 +12781,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Air Jordan 1 Low OG Sail / Off White</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12492,17 +12813,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -12510,7 +12831,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12522,17 +12843,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Nike Air Max 95 SE 'England'</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -12540,7 +12861,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12873,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12562,7 +12883,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -12570,19 +12891,19 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12592,351 +12913,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 Oregon Ducks</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Converse Kentucky Wildcats 30th Anniversary</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Reebok Angel Navy Halo</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Chicago</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail / Off White</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike GT Future Unseen Hours</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike G.t. Cut 1 Orange Pulse / Persian Violet</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike G.t. Future Unseen Hours</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12951,7 +12936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q108"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13084,12 +13069,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -13108,13 +13093,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-grey-matter-u20004jq/705427</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-dark-team-red-patent-leather-pack-io4489-601/706787</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>50</v>
@@ -13145,12 +13130,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -13169,13 +13154,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-ice-wine-u20002t8/705920</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-mystic-navy-patent-leather-pack-io4489-400/706786</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
         <v>50</v>
@@ -13211,14 +13196,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -13234,7 +13215,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-vomero-premium-black-iq0627-001/705450</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-topaz-gold-patent-leather-pack-io4489-700/706785</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -13703,7 +13684,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13723,12 +13704,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -13746,13 +13727,13 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P12" t="n">
         <v>50</v>
@@ -13773,7 +13754,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -13788,7 +13769,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -13807,11 +13788,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -13820,7 +13801,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -13838,7 +13819,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -13853,26 +13834,30 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -13881,7 +13866,7 @@
         <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -13909,23 +13894,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -13933,13 +13918,13 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
+          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
         <v>50</v>
@@ -13975,7 +13960,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
+          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -13994,7 +13979,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -14036,7 +14021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -14055,7 +14040,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -14092,23 +14077,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Converse Shai 001 Pink</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -14116,7 +14101,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -14134,7 +14119,7 @@
         <v>46093</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -14158,18 +14143,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Converse Shai 001 Pink</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -14177,7 +14162,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
+          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -14204,7 +14189,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -14219,39 +14204,35 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -14269,7 +14250,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -14279,12 +14260,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -14303,11 +14284,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -14316,7 +14297,7 @@
         <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -14344,23 +14325,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -14368,13 +14353,13 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P22" t="n">
         <v>50</v>
@@ -14410,7 +14395,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -14429,7 +14414,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -14456,7 +14441,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14471,26 +14456,26 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>New Balance 1890 Faded Black / Utility Green</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -14499,7 +14484,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -14517,7 +14502,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -14532,26 +14517,26 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>New Balance 1890 Faded Black / Utility Green</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -14560,7 +14545,7 @@
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -14573,7 +14558,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -14588,27 +14573,23 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -14616,13 +14597,13 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
         <v>50</v>
@@ -14643,12 +14624,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -14658,30 +14639,30 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -14690,7 +14671,7 @@
         <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -14703,17 +14684,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -14723,35 +14704,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Kobe 3 Low Protro Pink Quartz</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -14784,7 +14769,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -14803,7 +14788,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -14845,18 +14830,18 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -14864,7 +14849,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -17439,7 +17424,7 @@
         <v>46095</v>
       </c>
       <c r="B72" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -19326,7 +19311,7 @@
     </row>
     <row r="102">
       <c r="A102" s="14" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -19348,12 +19333,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -19372,13 +19357,13 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-team-usa-iq0407-100/706740</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P102" t="n">
         <v>50</v>
@@ -19387,14 +19372,14 @@
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -19409,15 +19394,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Nike Air Max 95 SE 'England'</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -19433,13 +19422,13 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-se-england-iq0176-100/706661</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P103" t="n">
         <v>50</v>
@@ -19448,14 +19437,14 @@
     </row>
     <row r="104">
       <c r="A104" s="14" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -19475,12 +19464,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -19498,13 +19487,13 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-plus-french-football-federation-iq0170-400/706739</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P104" t="n">
         <v>50</v>
@@ -19535,12 +19524,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -19559,13 +19548,13 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P105" t="n">
         <v>50</v>
@@ -19581,7 +19570,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -19596,19 +19585,15 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>collab, running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -19624,13 +19609,13 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="P106" t="n">
         <v>50</v>
@@ -19639,14 +19624,14 @@
     </row>
     <row r="107">
       <c r="A107" s="14" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B107" t="n">
         <v>0</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -19666,18 +19651,22 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -19685,13 +19674,13 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="P107" t="n">
         <v>50</v>
@@ -19700,7 +19689,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -19727,7 +19716,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -19746,7 +19735,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -19758,6 +19747,132 @@
         <v>50</v>
       </c>
       <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>collab, running, exclusive</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>40</v>
+      </c>
+      <c r="P109" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>12</v>
+      </c>
+      <c r="P110" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19939,7 +20054,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -19949,7 +20064,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5"/>
@@ -19967,7 +20082,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -19977,7 +20092,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -20007,7 +20122,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -20085,7 +20200,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -20123,7 +20238,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26">
